--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4427.89</v>
+        <v>4390.39</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1647.72</v>
+        <v>1639.25</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>602.8200000000001</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>313.37</v>
+        <v>311.65</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>472.93</v>
+        <v>470.34</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1227.01</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1405.32</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>83.77</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3055.32</v>
+        <v>3065.37</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>285.88</v>
+        <v>290.82</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1077.2</v>
+        <v>1084.66</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>538.6</v>
+        <v>541.11</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>273.92</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1559.28</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>435.63</v>
+        <v>431.29</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3223.34</v>
+        <v>3209.83</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>290.69</v>
+        <v>292.01</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>575.39</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>629.83</v>
+        <v>628.95</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1531</v>
+        <v>1541.53</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2662.74</v>
+        <v>2685.49</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3199.07</v>
+        <v>3136.67</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>665.03</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>811.98</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5088.66</v>
+        <v>5061.78</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>47512.72</v>
+        <v>47824.12</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>165.26</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3745.9</v>
+        <v>3802.93</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>600.95</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2275.03</v>
+        <v>2266.93</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>403.1</v>
+        <v>400.08</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1108.52</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>379.87</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3124.02</v>
+        <v>3110.85</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>806.2</v>
+        <v>802.8</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>374.75</v>
+        <v>372.07</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3676.05</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1769.22</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>982.9</v>
+        <v>981.45</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4355.75</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>589.74</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>345.95</v>
+        <v>344.06</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>296.53</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4843.27</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3384.63</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>607.79</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>420.78</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>200.77</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>44.27</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>60.84</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>73.68000000000001</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>596.38</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3386.17</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1032.94</v>
+        <v>1026.32</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>336.25</v>
+        <v>329.02</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1031.59</v>
+        <v>998.7</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>301.38</v>
+        <v>293.44</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>734.77</v>
+        <v>736.9</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4390.04</v>
+        <v>4427.3</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>381.87</v>
+        <v>385.11</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>205.97</v>
+        <v>205.63</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1312.08</v>
+        <v>1328.23</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1266.36</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>357.05</v>
+        <v>361.7</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>238.03</v>
+        <v>240.74</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5600.87</v>
+        <v>5651.32</v>
       </c>
     </row>
     <row r="68">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1109.53</v>
+        <v>1113.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3483-148-CM26</t>
+          <t>3459-112-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>664.5</v>
+        <v>3207.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3459-112-CM26</t>
+          <t>3483-148-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3194.06</v>
+        <v>667.26</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>468.64</v>
+        <v>469.61</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>702.96</v>
+        <v>699.9400000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4314.36</v>
+        <v>4277.56</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>419.45</v>
+        <v>421.71</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1198.43</v>
+        <v>1204.89</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3262.06</v>
+        <v>3298.54</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5217.96</v>
+        <v>5204.79</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>201.29</v>
+        <v>202.79</v>
       </c>
     </row>
     <row r="79">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>161.4</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1193663-23-CM26</t>
+          <t>1093870-5-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1285.93</v>
+        <v>465.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1173041-18-CM26</t>
+          <t>5738-23-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>774.74</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1093870-5-CM26</t>
+          <t>1193663-23-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>463.4</v>
+        <v>1292.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5738-23-CM26</t>
+          <t>1173041-18-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>428.18</v>
+        <v>778.55</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>801.88</v>
+        <v>804.54</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2459.49</v>
+        <v>2494.68</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4504.59</v>
+        <v>4557.43</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>201.09</v>
+        <v>204.49</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>539.59</v>
+        <v>545.08</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>695.52</v>
+        <v>702.04</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2921.52</v>
+        <v>2880.06</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>354.08</v>
+        <v>351.89</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2124.49</v>
+        <v>2111.32</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>147.53</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="94">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>424.9</v>
+        <v>426.83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1110404-553-CM26</t>
+          <t>3340-159-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>236.05</v>
+        <v>3307.46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3340-159-CM26</t>
+          <t>1110404-553-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3245.75</v>
+        <v>240.54</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1340.29</v>
+        <v>1370.52</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>744.28</v>
+        <v>749.42</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1499.45</v>
+        <v>1504.09</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1153.93</v>
+        <v>1138.56</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>692.36</v>
+        <v>682.1</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4507.42</v>
+        <v>4550.24</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>235.42</v>
+        <v>236.33</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4915.59</v>
+        <v>4926.06</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>641.16</v>
+        <v>645.46</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1931.93</v>
+        <v>1927.72</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>427.44</v>
+        <v>426.59</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2971.9</v>
+        <v>2955.42</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3998.32</v>
+        <v>4025.09</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,68 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>136.45</v>
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5702-578-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1043.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3340-356-CM25</t>
+          <t>1173041-62-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4390.39</v>
+        <v>640.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1075963-51923-CM25</t>
+          <t>707409-111-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1639.25</v>
+        <v>123.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4232-156-CM25</t>
+          <t>1193663-45-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>599.53</v>
+        <v>696.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-368-CM25</t>
+          <t>1173041-66-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>311.65</v>
+        <v>505.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079596-337-CM25</t>
+          <t>3340-356-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>470.34</v>
+        <v>4390.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3340-352-CM25</t>
+          <t>1075963-51923-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1225.45</v>
+        <v>1639.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1346279-200-CM25</t>
+          <t>4232-156-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1403.53</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5951-5602-CM25</t>
+          <t>2021-368-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>84.06999999999999</v>
+        <v>311.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5702-873-CM25</t>
+          <t>1079596-337-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3065.37</v>
+        <v>470.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079596-356-CM25</t>
+          <t>3340-352-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>290.82</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5702-882-CM25</t>
+          <t>1346279-200-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1084.66</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1173041-74-CM25</t>
+          <t>5951-5602-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>541.11</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1087-353-CM25</t>
+          <t>5702-873-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>275.85</v>
+        <v>3065.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>720-1086-CM25</t>
+          <t>1079596-356-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1570.28</v>
+        <v>290.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3459-319-CM25</t>
+          <t>5702-882-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>431.29</v>
+        <v>1084.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5702-946-CM25</t>
+          <t>1173041-74-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3209.83</v>
+        <v>541.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1250615-15-CM25</t>
+          <t>720-1086-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>292.01</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3185-172-CM25</t>
+          <t>1087-353-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>576.92</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1173041-79-CM25</t>
+          <t>3459-319-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>628.95</v>
+        <v>431.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1087-381-CM25</t>
+          <t>5702-946-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1541.53</v>
+        <v>3209.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3459-328-CM25</t>
+          <t>1250615-15-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2685.49</v>
+        <v>292.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5702-995-CM25</t>
+          <t>3185-172-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3136.67</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1173041-1-CM26</t>
+          <t>1173041-79-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>656.58</v>
+        <v>628.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3390-5-CM26</t>
+          <t>1087-381-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>810.38</v>
+        <v>1541.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3340-3-CM26</t>
+          <t>3459-328-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5061.78</v>
+        <v>2685.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079596-7-CM26</t>
+          <t>5702-995-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>47824.12</v>
+        <v>3136.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4232-7-CM26</t>
+          <t>1173041-1-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>167.49</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5702-25-CM26</t>
+          <t>3390-5-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3802.93</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1173041-2-CM26</t>
+          <t>3340-3-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>619.17</v>
+        <v>5061.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3390-19-CM26</t>
+          <t>1079596-7-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2266.93</v>
+        <v>47824.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5702-58-CM26</t>
+          <t>4232-7-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>400.08</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5702-61-CM26</t>
+          <t>5702-25-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1100.23</v>
+        <v>3802.93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>963423-6-CM26</t>
+          <t>1173041-2-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>380.97</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3340-13-CM26</t>
+          <t>3390-19-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3110.85</v>
+        <v>2266.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3340-14-CM26</t>
+          <t>5702-58-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>802.8</v>
+        <v>400.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3185-22-CM26</t>
+          <t>5702-61-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>372.07</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5702-85-CM26</t>
+          <t>963423-6-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Zona de Bienestar Arica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3649.71</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1075963-2476-CM26</t>
+          <t>3340-13-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1756.55</v>
+        <v>3110.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3340-20-CM26</t>
+          <t>3340-14-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>981.45</v>
+        <v>802.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3340-21-CM26</t>
+          <t>5702-85-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4349.35</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1173041-5-CM26</t>
+          <t>1075963-2476-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>588.87</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4232-23-CM26</t>
+          <t>3185-22-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>344.06</v>
+        <v>372.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1173457-6-CM26</t>
+          <t>1173041-5-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>298.06</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3340-32-CM26</t>
+          <t>3340-20-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4847.94</v>
+        <v>981.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3340-33-CM26</t>
+          <t>3340-21-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3387.89</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1317925-11-CM26</t>
+          <t>4232-23-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>608.37</v>
+        <v>344.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1087-19-CM26</t>
+          <t>1173457-6-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>433</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3483-80-CM26</t>
+          <t>3340-32-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>199.35</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1572-23-CM26</t>
+          <t>3340-33-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>45.08</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>838099-21-CM26</t>
+          <t>1317925-11-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>61.79</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>838099-22-CM26</t>
+          <t>1087-19-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>74.83</v>
+        <v>433</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1173041-9-CM26</t>
+          <t>3483-80-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>596.35</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5702-151-CM26</t>
+          <t>1572-23-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3386</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3340-42-CM26</t>
+          <t>838099-21-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Zona Bienestar "Arica" Bienestar Social</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1026.32</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079596-50-CM26</t>
+          <t>838099-22-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Zona Bienestar "Arica" Bienestar Social</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>329.02</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>720-86-CM26</t>
+          <t>1173041-9-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>998.7</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4232-44-CM26</t>
+          <t>5702-151-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>293.44</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1173041-13-CM26</t>
+          <t>3340-42-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>736.9</v>
+        <v>1026.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5702-255-CM26</t>
+          <t>1079596-50-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4427.3</v>
+        <v>329.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079596-57-CM26</t>
+          <t>720-86-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>385.11</v>
+        <v>998.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3340-62-CM26</t>
+          <t>4232-44-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>205.63</v>
+        <v>293.44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3483-119-CM26</t>
+          <t>1173041-13-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1328.23</v>
+        <v>736.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5702-263-CM26</t>
+          <t>5702-255-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1281.94</v>
+        <v>4427.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1173457-15-CM26</t>
+          <t>1079596-57-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>361.7</v>
+        <v>385.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1110404-334-CM26</t>
+          <t>3340-62-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>240.74</v>
+        <v>205.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3340-93-CM26</t>
+          <t>3483-119-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5651.32</v>
+        <v>1328.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3390-138-CM26</t>
+          <t>5702-263-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1113.02</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3459-112-CM26</t>
+          <t>1173457-15-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3207.3</v>
+        <v>361.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3483-148-CM26</t>
+          <t>1110404-334-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>667.26</v>
+        <v>240.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5702-294-CM26</t>
+          <t>3340-93-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>469.61</v>
+        <v>5651.32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1173041-15-CM26</t>
+          <t>3390-138-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>699.9400000000001</v>
+        <v>1113.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5702-319-CM26</t>
+          <t>3483-148-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4277.56</v>
+        <v>667.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4232-50-CM26</t>
+          <t>3459-112-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>421.71</v>
+        <v>3207.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3340-114-CM26</t>
+          <t>5702-294-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1204.89</v>
+        <v>469.61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1110404-391-CM26</t>
+          <t>1173041-15-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3298.54</v>
+        <v>699.9400000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3340-121-CM26</t>
+          <t>5702-319-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5204.79</v>
+        <v>4277.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5951-48-CM26</t>
+          <t>4232-50-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>202.79</v>
+        <v>421.71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>707409-53-CM26</t>
+          <t>3340-114-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>162.2</v>
+        <v>1204.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1093870-5-CM26</t>
+          <t>1110404-391-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>465.68</v>
+        <v>3298.54</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5738-23-CM26</t>
+          <t>3340-121-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>430.28</v>
+        <v>5204.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1193663-23-CM26</t>
+          <t>5951-48-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1292.25</v>
+        <v>202.79</v>
       </c>
     </row>
     <row r="83">
@@ -5516,7 +5516,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1774-61-CM26</t>
+          <t>707409-53-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>804.54</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3390-222-CM26</t>
+          <t>1193663-23-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2494.68</v>
+        <v>1292.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5702-379-CM26</t>
+          <t>5738-23-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4557.43</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3340-143-CM26</t>
+          <t>1093870-5-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>204.49</v>
+        <v>465.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1087-120-CM26</t>
+          <t>1774-61-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>545.08</v>
+        <v>804.54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1173041-23-CM26</t>
+          <t>3390-222-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>702.04</v>
+        <v>2494.68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3340-135-CM26</t>
+          <t>5702-379-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2880.06</v>
+        <v>4557.43</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1173457-25-CM26</t>
+          <t>3340-143-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>351.89</v>
+        <v>204.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1075963-7798-CM26</t>
+          <t>1087-120-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2111.32</v>
+        <v>545.08</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>707409-58-CM26</t>
+          <t>1173041-23-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>148.2</v>
+        <v>702.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4232-66-CM26</t>
+          <t>3340-135-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>426.83</v>
+        <v>2880.06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3340-159-CM26</t>
+          <t>1173457-25-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3307.46</v>
+        <v>351.89</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1110404-553-CM26</t>
+          <t>1075963-7798-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>240.54</v>
+        <v>2111.32</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3483-226-CM26</t>
+          <t>707409-58-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1370.52</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3340-162-CM26</t>
+          <t>4232-66-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>749.42</v>
+        <v>426.83</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3483-217-CM26</t>
+          <t>1110404-553-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1504.09</v>
+        <v>240.54</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5702-455-CM26</t>
+          <t>3340-159-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1138.56</v>
+        <v>3307.46</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1173041-29-CM26</t>
+          <t>3483-226-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>682.1</v>
+        <v>1370.52</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5702-467-CM26</t>
+          <t>3340-162-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4550.24</v>
+        <v>749.42</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>963423-156-CM26</t>
+          <t>3483-217-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>236.33</v>
+        <v>1504.09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3340-184-CM26</t>
+          <t>5702-455-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4926.06</v>
+        <v>1138.56</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1173041-36-CM26</t>
+          <t>1173041-29-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>645.46</v>
+        <v>682.1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1346279-91-CM26</t>
+          <t>5702-467-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1927.72</v>
+        <v>4550.24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5702-515-CM26</t>
+          <t>963423-156-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Zona de Bienestar Arica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>426.59</v>
+        <v>236.33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3459-194-CM26</t>
+          <t>3340-184-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2955.42</v>
+        <v>4926.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5702-528-CM26</t>
+          <t>1173041-36-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4025.09</v>
+        <v>645.46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>707409-74-CM26</t>
+          <t>1346279-91-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>137.37</v>
+        <v>1927.72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5702-578-CM26</t>
+          <t>5702-515-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,6 +7218,250 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
+        <v>426.59</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3459-194-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>2955.42</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>707409-74-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>5702-528-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>4025.09</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>5702-578-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
         <v>1043.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1173041-62-CM25</t>
+          <t>5702-528-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>640.86</v>
+        <v>3301.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707409-111-CM25</t>
+          <t>1110404-883-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>123.24</v>
+        <v>452.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1193663-45-CM25</t>
+          <t>1079596-181-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>696.9</v>
+        <v>341.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1173041-66-CM25</t>
+          <t>3483-174-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>505.51</v>
+        <v>1140.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3340-356-CM25</t>
+          <t>1173041-47-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4390.39</v>
+        <v>668.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1075963-51923-CM25</t>
+          <t>3340-248-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1639.25</v>
+        <v>1323.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4232-156-CM25</t>
+          <t>3340-249-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>599.53</v>
+        <v>2976.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-368-CM25</t>
+          <t>837-388-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>311.65</v>
+        <v>349.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079596-337-CM25</t>
+          <t>5702-585-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>470.34</v>
+        <v>4249.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3340-352-CM25</t>
+          <t>3390-268-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1225.45</v>
+        <v>3297.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1346279-200-CM25</t>
+          <t>5702-598-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1403.53</v>
+        <v>404.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5951-5602-CM25</t>
+          <t>1110404-1004-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>84.06999999999999</v>
+        <v>1124.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5702-873-CM25</t>
+          <t>3340-261-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3065.37</v>
+        <v>2262.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079596-356-CM25</t>
+          <t>3340-262-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>290.82</v>
+        <v>616.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5702-882-CM25</t>
+          <t>837-415-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1084.66</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1173041-74-CM25</t>
+          <t>838099-77-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>541.11</v>
+        <v>307.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>720-1086-CM25</t>
+          <t>3340-279-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1570.28</v>
+        <v>5086.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1087-353-CM25</t>
+          <t>1173041-49-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>275.85</v>
+        <v>662.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3459-319-CM25</t>
+          <t>1572-280-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>431.29</v>
+        <v>185.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5702-946-CM25</t>
+          <t>3459-260-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3209.83</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1250615-15-CM25</t>
+          <t>5702-642-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>292.01</v>
+        <v>3379.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3185-172-CM25</t>
+          <t>1173457-38-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>576.92</v>
+        <v>227.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1173041-79-CM25</t>
+          <t>5702-698-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>628.95</v>
+        <v>1039.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1087-381-CM25</t>
+          <t>4232-117-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1541.53</v>
+        <v>596.5599999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3459-328-CM25</t>
+          <t>5750-94-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2685.49</v>
+        <v>1552.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5702-995-CM25</t>
+          <t>3340-296-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3136.67</v>
+        <v>3244.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1173041-1-CM26</t>
+          <t>1173041-58-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>656.58</v>
+        <v>653.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3390-5-CM26</t>
+          <t>3459-271-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>810.38</v>
+        <v>2639.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3340-3-CM26</t>
+          <t>838099-83-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5061.78</v>
+        <v>333.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1079596-7-CM26</t>
+          <t>3185-115-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>47824.12</v>
+        <v>286.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4232-7-CM26</t>
+          <t>548849-83-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>167.49</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5702-25-CM26</t>
+          <t>837-513-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3802.93</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1173041-2-CM26</t>
+          <t>3340-304-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>619.17</v>
+        <v>1268.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3390-19-CM26</t>
+          <t>5702-733-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2266.93</v>
+        <v>3763.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5702-58-CM26</t>
+          <t>963423-2668-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>400.08</v>
+        <v>702.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5702-61-CM26</t>
+          <t>707409-111-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1100.23</v>
+        <v>123.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>963423-6-CM26</t>
+          <t>1173041-62-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>380.97</v>
+        <v>640.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3340-13-CM26</t>
+          <t>3483-230-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3110.85</v>
+        <v>1301.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3340-14-CM26</t>
+          <t>1193663-45-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>802.8</v>
+        <v>696.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5702-85-CM26</t>
+          <t>3340-322-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3649.71</v>
+        <v>4177.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1075963-2476-CM26</t>
+          <t>3340-331-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1756.55</v>
+        <v>3054.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3185-22-CM26</t>
+          <t>837-568-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>372.07</v>
+        <v>276.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1173041-5-CM26</t>
+          <t>1250615-1-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>588.87</v>
+        <v>224.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3340-20-CM26</t>
+          <t>5702-807-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>981.45</v>
+        <v>3339.87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3340-21-CM26</t>
+          <t>3340-332-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4349.35</v>
+        <v>809.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4232-23-CM26</t>
+          <t>3340-342-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>344.06</v>
+        <v>3689.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1173457-6-CM26</t>
+          <t>5702-828-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>298.06</v>
+        <v>405.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3340-32-CM26</t>
+          <t>1173041-66-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4847.94</v>
+        <v>505.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3340-33-CM26</t>
+          <t>837-628-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3387.89</v>
+        <v>235.33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1317925-11-CM26</t>
+          <t>3340-356-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>608.37</v>
+        <v>4390.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1087-19-CM26</t>
+          <t>1075963-51923-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>433</v>
+        <v>1639.25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3483-80-CM26</t>
+          <t>4232-156-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>199.35</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1572-23-CM26</t>
+          <t>1079596-337-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>45.08</v>
+        <v>470.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>838099-21-CM26</t>
+          <t>2021-368-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>61.79</v>
+        <v>311.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>838099-22-CM26</t>
+          <t>3340-352-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>74.83</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1173041-9-CM26</t>
+          <t>1346279-200-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>596.35</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5702-151-CM26</t>
+          <t>5951-5602-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3386</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3340-42-CM26</t>
+          <t>5702-873-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1026.32</v>
+        <v>3065.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079596-50-CM26</t>
+          <t>1079596-356-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>329.02</v>
+        <v>290.82</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>720-86-CM26</t>
+          <t>5702-882-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>998.7</v>
+        <v>1084.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4232-44-CM26</t>
+          <t>1173041-74-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>293.44</v>
+        <v>541.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1173041-13-CM26</t>
+          <t>720-1086-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>736.9</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5702-255-CM26</t>
+          <t>1087-353-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4427.3</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1079596-57-CM26</t>
+          <t>3459-319-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>385.11</v>
+        <v>431.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3340-62-CM26</t>
+          <t>5702-946-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>205.63</v>
+        <v>3209.83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3483-119-CM26</t>
+          <t>1250615-15-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1328.23</v>
+        <v>292.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5702-263-CM26</t>
+          <t>3185-172-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1281.94</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1173457-15-CM26</t>
+          <t>1173041-79-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>361.7</v>
+        <v>628.95</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1110404-334-CM26</t>
+          <t>1087-381-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>240.74</v>
+        <v>1541.53</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3340-93-CM26</t>
+          <t>3459-328-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5651.32</v>
+        <v>2685.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3390-138-CM26</t>
+          <t>5702-995-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1113.02</v>
+        <v>3136.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3483-148-CM26</t>
+          <t>1173041-1-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>667.26</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3459-112-CM26</t>
+          <t>3390-5-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3207.3</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5702-294-CM26</t>
+          <t>3340-3-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>469.61</v>
+        <v>5061.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1173041-15-CM26</t>
+          <t>1079596-7-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>699.9400000000001</v>
+        <v>47824.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5702-319-CM26</t>
+          <t>4232-7-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5099,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4277.56</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4232-50-CM26</t>
+          <t>5702-25-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>421.71</v>
+        <v>3802.93</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3340-114-CM26</t>
+          <t>1173041-2-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1204.89</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1110404-391-CM26</t>
+          <t>3390-19-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3298.54</v>
+        <v>2266.93</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3340-121-CM26</t>
+          <t>5702-58-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5204.79</v>
+        <v>400.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5951-48-CM26</t>
+          <t>5702-61-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>202.79</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1173041-18-CM26</t>
+          <t>963423-6-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Zona de Bienestar Arica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>778.55</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>707409-53-CM26</t>
+          <t>3340-14-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>162.2</v>
+        <v>802.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1193663-23-CM26</t>
+          <t>3340-13-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1292.25</v>
+        <v>3110.85</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5738-23-CM26</t>
+          <t>3185-22-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>430.28</v>
+        <v>372.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1093870-5-CM26</t>
+          <t>5702-85-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,27 +5709,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>465.68</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1774-61-CM26</t>
+          <t>1075963-2476-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>804.54</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3390-222-CM26</t>
+          <t>1173041-5-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2494.68</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5702-379-CM26</t>
+          <t>3340-20-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4557.43</v>
+        <v>981.45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3340-143-CM26</t>
+          <t>3340-21-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>204.49</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1087-120-CM26</t>
+          <t>4232-23-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>545.08</v>
+        <v>344.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1173041-23-CM26</t>
+          <t>1173457-6-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>702.04</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3340-135-CM26</t>
+          <t>1317925-11-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2880.06</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1173457-25-CM26</t>
+          <t>3340-32-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>351.89</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1075963-7798-CM26</t>
+          <t>3340-33-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,27 +6258,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2111.32</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707409-58-CM26</t>
+          <t>1087-19-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>148.2</v>
+        <v>433</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4232-66-CM26</t>
+          <t>3483-80-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>426.83</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1110404-553-CM26</t>
+          <t>1572-23-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>240.54</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3340-159-CM26</t>
+          <t>838099-21-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Zona Bienestar "Arica" Bienestar Social</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3307.46</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3483-226-CM26</t>
+          <t>838099-22-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Zona Bienestar "Arica" Bienestar Social</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1370.52</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3340-162-CM26</t>
+          <t>1173041-9-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>749.42</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3483-217-CM26</t>
+          <t>5702-151-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1504.09</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5702-455-CM26</t>
+          <t>3340-42-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1138.56</v>
+        <v>1026.32</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1173041-29-CM26</t>
+          <t>1079596-50-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>682.1</v>
+        <v>329.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5702-467-CM26</t>
+          <t>720-86-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4550.24</v>
+        <v>998.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>963423-156-CM26</t>
+          <t>4232-44-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>236.33</v>
+        <v>293.44</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3340-184-CM26</t>
+          <t>1173041-13-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4926.06</v>
+        <v>736.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1173041-36-CM26</t>
+          <t>5702-255-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,27 +7051,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>645.46</v>
+        <v>4427.3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1346279-91-CM26</t>
+          <t>1079596-57-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,27 +7112,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1927.72</v>
+        <v>385.11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5702-515-CM26</t>
+          <t>3340-62-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>426.59</v>
+        <v>205.63</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3459-194-CM26</t>
+          <t>3483-119-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2955.42</v>
+        <v>1328.23</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>707409-74-CM26</t>
+          <t>5702-263-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>137.37</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5702-528-CM26</t>
+          <t>1173457-15-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7356,27 +7356,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4025.09</v>
+        <v>361.7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5702-578-CM26</t>
+          <t>1110404-334-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,7 +7462,3301 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
+        <v>240.74</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>3340-93-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>5651.32</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3390-138-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1113.02</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3483-148-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>667.26</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3459-112-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>3207.3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>5702-294-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>469.61</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1173041-15-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>699.9400000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>5702-319-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>4277.56</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4232-50-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>421.71</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>3340-114-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>1204.89</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1110404-391-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>3298.54</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3340-121-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>5204.79</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>5951-48-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>202.79</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1093870-5-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>65.184.303-0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>465.68</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>5738-23-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>60.908.000-0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>430.28</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1193663-23-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>61.978.970-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>1292.25</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>707409-53-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>162.2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1173041-18-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>778.55</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1774-61-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>60.804.001-3</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>804.54</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3390-222-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>2494.68</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>5702-379-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>4557.43</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>3340-143-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>204.49</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1087-120-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>545.08</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1173041-23-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>702.04</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>3340-135-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>2880.06</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1173457-25-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>75.554.600-3</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>351.89</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1075963-7798-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>2111.32</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>707409-58-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>148.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4232-66-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>426.83</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>3340-159-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>3307.46</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1110404-553-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>240.54</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>3483-226-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>1370.52</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3340-162-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>749.42</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>3483-217-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>1504.09</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>5702-455-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>1138.56</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1173041-29-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>682.1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>5702-467-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>4550.24</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>963423-156-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.980.850-9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Arica</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>236.33</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3340-184-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>4926.06</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1173041-36-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Prisión Arica</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>645.46</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1346279-91-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>1927.72</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>5702-515-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>426.59</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>3459-194-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>2955.42</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>5702-528-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>4025.09</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>707409-74-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1173457-29-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>75.554.600-3</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>328.38</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1173041-38-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>667.23</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>837-514-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.003.000-9</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>312.45</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>3340-212-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>5457.4</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>5702-578-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
         <v>1043.71</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>963423-196-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.980.850-9</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>738.26</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>5702-593-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>3383.85</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1173041-41-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>622.01</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3340-225-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>1036.68</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>3483-282-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>1954.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3390-268-CM25</t>
+          <t>5702-598-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3297.9</v>
+        <v>404.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5702-598-CM25</t>
+          <t>1110404-1004-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>404.55</v>
+        <v>1124.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1110404-1004-CM25</t>
+          <t>3390-268-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1124.05</v>
+        <v>3297.9</v>
       </c>
     </row>
     <row r="14">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4232-156-CM25</t>
+          <t>1079596-337-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>599.53</v>
+        <v>470.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079596-337-CM25</t>
+          <t>4232-156-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>470.34</v>
+        <v>599.53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2021-368-CM25</t>
+          <t>3340-352-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>311.65</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3340-352-CM25</t>
+          <t>1346279-200-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1225.45</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1346279-200-CM25</t>
+          <t>5951-5602-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1403.53</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5951-5602-CM25</t>
+          <t>5702-873-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>84.06999999999999</v>
+        <v>3065.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5702-873-CM25</t>
+          <t>1079596-356-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3065.37</v>
+        <v>290.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079596-356-CM25</t>
+          <t>5702-882-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>290.82</v>
+        <v>1084.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5702-882-CM25</t>
+          <t>1173041-74-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1084.66</v>
+        <v>541.11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1173041-74-CM25</t>
+          <t>1087-353-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>541.11</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="63">
@@ -4296,7 +4296,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1087-353-CM25</t>
+          <t>3459-319-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>275.85</v>
+        <v>431.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3459-319-CM25</t>
+          <t>5702-946-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>431.29</v>
+        <v>3209.83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5702-946-CM25</t>
+          <t>1250615-15-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3209.83</v>
+        <v>292.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1250615-15-CM25</t>
+          <t>3185-172-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>292.01</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3185-172-CM25</t>
+          <t>1173041-79-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>576.92</v>
+        <v>628.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1173041-79-CM25</t>
+          <t>1087-381-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>628.95</v>
+        <v>1541.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1087-381-CM25</t>
+          <t>3459-328-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1541.53</v>
+        <v>2685.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3459-328-CM25</t>
+          <t>5702-995-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2685.49</v>
+        <v>3136.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5702-995-CM25</t>
+          <t>1173041-1-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3136.67</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1173041-1-CM26</t>
+          <t>3390-5-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>656.58</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3390-5-CM26</t>
+          <t>3340-3-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>810.38</v>
+        <v>5061.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3340-3-CM26</t>
+          <t>1079596-7-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5061.78</v>
+        <v>47824.12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1079596-7-CM26</t>
+          <t>4232-7-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>47824.12</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4232-7-CM26</t>
+          <t>5702-25-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>167.49</v>
+        <v>3802.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5702-25-CM26</t>
+          <t>1173041-2-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3802.93</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1173041-2-CM26</t>
+          <t>3390-19-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>619.17</v>
+        <v>2266.93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3390-19-CM26</t>
+          <t>5702-61-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2266.93</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="81">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5394,7 +5394,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5702-61-CM26</t>
+          <t>963423-6-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1100.23</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>963423-6-CM26</t>
+          <t>3340-13-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>380.97</v>
+        <v>3110.85</v>
       </c>
     </row>
     <row r="84">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5577,7 +5577,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3340-13-CM26</t>
+          <t>3185-22-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3110.85</v>
+        <v>372.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3185-22-CM26</t>
+          <t>5702-85-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,17 +5658,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>372.07</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5702-85-CM26</t>
+          <t>1075963-2476-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3649.71</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-2476-CM26</t>
+          <t>3340-20-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1756.55</v>
+        <v>981.45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1173041-5-CM26</t>
+          <t>3340-21-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>588.87</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3340-20-CM26</t>
+          <t>1173041-5-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>981.45</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3340-21-CM26</t>
+          <t>4232-23-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4349.35</v>
+        <v>344.06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4232-23-CM26</t>
+          <t>1173457-6-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>344.06</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1173457-6-CM26</t>
+          <t>3340-32-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>298.06</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1317925-11-CM26</t>
+          <t>3340-33-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>608.37</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3340-32-CM26</t>
+          <t>1317925-11-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4847.94</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3340-33-CM26</t>
+          <t>1087-19-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3387.89</v>
+        <v>433</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1087-19-CM26</t>
+          <t>3483-80-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>433</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3483-80-CM26</t>
+          <t>1572-23-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>199.35</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1572-23-CM26</t>
+          <t>838099-21-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>45.08</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>838099-21-CM26</t>
+          <t>838099-22-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>61.79</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>838099-22-CM26</t>
+          <t>5702-151-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>74.83</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="102">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6675,7 +6675,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5702-151-CM26</t>
+          <t>3340-42-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3386</v>
+        <v>1026.32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3340-42-CM26</t>
+          <t>1079596-50-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1026.32</v>
+        <v>329.02</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079596-50-CM26</t>
+          <t>720-86-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>329.02</v>
+        <v>998.7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>720-86-CM26</t>
+          <t>4232-44-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>998.7</v>
+        <v>293.44</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4232-44-CM26</t>
+          <t>1173041-13-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>293.44</v>
+        <v>736.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1173041-13-CM26</t>
+          <t>5702-255-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>736.9</v>
+        <v>4427.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5702-255-CM26</t>
+          <t>1079596-57-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4427.3</v>
+        <v>385.11</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079596-57-CM26</t>
+          <t>3340-62-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>385.11</v>
+        <v>205.63</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3340-62-CM26</t>
+          <t>3483-119-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>205.63</v>
+        <v>1328.23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3483-119-CM26</t>
+          <t>5702-263-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1328.23</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5702-263-CM26</t>
+          <t>1173457-15-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1281.94</v>
+        <v>361.7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1173457-15-CM26</t>
+          <t>1110404-334-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>361.7</v>
+        <v>240.74</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1110404-334-CM26</t>
+          <t>3340-93-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>240.74</v>
+        <v>5651.32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3340-93-CM26</t>
+          <t>3390-138-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5651.32</v>
+        <v>1113.02</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3390-138-CM26</t>
+          <t>3483-148-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1113.02</v>
+        <v>667.26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3483-148-CM26</t>
+          <t>3459-112-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>667.26</v>
+        <v>3207.3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3459-112-CM26</t>
+          <t>5702-294-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3207.3</v>
+        <v>469.61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5702-294-CM26</t>
+          <t>1173041-15-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>469.61</v>
+        <v>699.9400000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1173041-15-CM26</t>
+          <t>5702-319-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,27 +7783,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>699.9400000000001</v>
+        <v>4277.56</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5702-319-CM26</t>
+          <t>4232-50-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,22 +7849,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4277.56</v>
+        <v>421.71</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4232-50-CM26</t>
+          <t>3340-114-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>421.71</v>
+        <v>1204.89</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3340-114-CM26</t>
+          <t>1110404-391-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1204.89</v>
+        <v>3298.54</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1110404-391-CM26</t>
+          <t>3340-121-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3298.54</v>
+        <v>5204.79</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3340-121-CM26</t>
+          <t>5951-48-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5204.79</v>
+        <v>202.79</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5951-48-CM26</t>
+          <t>5738-23-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>202.79</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1093870-5-CM26</t>
+          <t>1193663-23-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>465.68</v>
+        <v>1292.25</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5738-23-CM26</t>
+          <t>707409-53-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>430.28</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1193663-23-CM26</t>
+          <t>1173041-18-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1292.25</v>
+        <v>778.55</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>707409-53-CM26</t>
+          <t>1774-61-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>162.2</v>
+        <v>804.54</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1173041-18-CM26</t>
+          <t>3390-222-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,27 +8454,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>778.55</v>
+        <v>2494.68</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1774-61-CM26</t>
+          <t>5702-379-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>804.54</v>
+        <v>4557.43</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3390-222-CM26</t>
+          <t>3340-143-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2494.68</v>
+        <v>204.49</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5702-379-CM26</t>
+          <t>1087-120-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4557.43</v>
+        <v>545.08</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3340-143-CM26</t>
+          <t>1173041-23-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>204.49</v>
+        <v>702.04</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1087-120-CM26</t>
+          <t>3340-135-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>545.08</v>
+        <v>2880.06</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1173041-23-CM26</t>
+          <t>1173457-25-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>702.04</v>
+        <v>351.89</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3340-135-CM26</t>
+          <t>1075963-7798-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,22 +8886,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2880.06</v>
+        <v>2111.32</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1173457-25-CM26</t>
+          <t>707409-58-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>351.89</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1075963-7798-CM26</t>
+          <t>4232-66-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,22 +9008,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2111.32</v>
+        <v>426.83</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>707409-58-CM26</t>
+          <t>3340-159-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>148.2</v>
+        <v>3307.46</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4232-66-CM26</t>
+          <t>1110404-553-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>426.83</v>
+        <v>240.54</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3340-159-CM26</t>
+          <t>3483-226-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3307.46</v>
+        <v>1370.52</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1110404-553-CM26</t>
+          <t>3340-162-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>240.54</v>
+        <v>749.42</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3483-226-CM26</t>
+          <t>3483-217-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1370.52</v>
+        <v>1504.09</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3340-162-CM26</t>
+          <t>5702-455-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>749.42</v>
+        <v>1138.56</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3483-217-CM26</t>
+          <t>1173041-29-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1504.09</v>
+        <v>682.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5702-455-CM26</t>
+          <t>5702-467-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1138.56</v>
+        <v>4550.24</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1173041-29-CM26</t>
+          <t>1053139-94-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>682.1</v>
+        <v>257.77</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5702-467-CM26</t>
+          <t>963423-156-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4550.24</v>
+        <v>236.33</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>963423-156-CM26</t>
+          <t>3340-184-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>236.33</v>
+        <v>4926.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3340-184-CM26</t>
+          <t>1173041-36-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4926.06</v>
+        <v>645.46</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1173041-36-CM26</t>
+          <t>1346279-91-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>645.46</v>
+        <v>1927.72</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1346279-91-CM26</t>
+          <t>5702-515-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,22 +9862,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1927.72</v>
+        <v>426.59</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5702-515-CM26</t>
+          <t>3185-97-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>426.59</v>
+        <v>471.22</v>
       </c>
     </row>
     <row r="157">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10213,7 +10213,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1173041-38-CM26</t>
+          <t>3390-294-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>667.23</v>
+        <v>1292.75</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>837-514-CM26</t>
+          <t>1173041-38-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>312.45</v>
+        <v>667.23</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3340-212-CM26</t>
+          <t>837-514-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5457.4</v>
+        <v>312.45</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5702-578-CM26</t>
+          <t>3340-212-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1043.71</v>
+        <v>5457.4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>963423-196-CM26</t>
+          <t>5702-578-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>738.26</v>
+        <v>1043.71</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5702-593-CM26</t>
+          <t>963423-196-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,22 +10533,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3383.85</v>
+        <v>738.26</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1173041-41-CM26</t>
+          <t>5702-593-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>622.01</v>
+        <v>3383.85</v>
       </c>
     </row>
     <row r="168">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3483-282-CM26</t>
+          <t>1173041-41-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,7 +10756,800 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
+        <v>622.01</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>3483-282-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
         <v>1954.15</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3348-95-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>176.59</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>3340-247-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>1548.26</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>3390-361-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>516.63</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>3390-362-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>3131.56</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1173041-56-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>612.54</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1173457-36-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>75.554.600-3</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>306.27</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1053139-139-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>172.73</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>3483-318-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>1070.9</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>3340-268-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>3995.57</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1075963-12353-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>1683.64</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>5702-688-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>4025.34</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1173041-60-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>597.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>720-49-CM25</t>
+          <t>2585-164-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>479.17</v>
+        <v>521.8200000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2585-164-CM25</t>
+          <t>720-49-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>521.8200000000001</v>
+        <v>479.17</v>
       </c>
     </row>
     <row r="12">
@@ -1294,7 +1294,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5702-113-CM25</t>
+          <t>3390-43-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1192.79</v>
+        <v>4649.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3390-43-CM25</t>
+          <t>5702-113-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4649.4</v>
+        <v>1192.79</v>
       </c>
     </row>
     <row r="16">
@@ -1554,7 +1554,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3390-61-CM25</t>
+          <t>3340-52-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>85.59</v>
+        <v>2743.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3340-52-CM25</t>
+          <t>3390-61-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2743.94</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="20">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3390-63-CM25</t>
+          <t>3483-47-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>995.21</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3483-47-CM25</t>
+          <t>3390-63-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1142</v>
+        <v>995.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>837-79-CM25</t>
+          <t>1173041-16-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3857.5</v>
+        <v>522.0599999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1173041-16-CM25</t>
+          <t>837-79-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>522.0599999999999</v>
+        <v>3857.5</v>
       </c>
     </row>
     <row r="25">
@@ -3504,7 +3504,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3340-149-CM25</t>
+          <t>1110404-438-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3138.65</v>
+        <v>190.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1110404-438-CM25</t>
+          <t>3340-149-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>190.06</v>
+        <v>3138.65</v>
       </c>
     </row>
     <row r="50">
@@ -3699,7 +3699,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1346279-80-CM25</t>
+          <t>1173041-35-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1127.67</v>
+        <v>613.5700000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1173041-35-CM25</t>
+          <t>1346279-80-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>613.5700000000001</v>
+        <v>1127.67</v>
       </c>
     </row>
     <row r="53">
@@ -5064,7 +5064,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1079596-181-CM25</t>
+          <t>1110404-883-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>341.23</v>
+        <v>452.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1110404-883-CM25</t>
+          <t>1079596-181-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>452.12</v>
+        <v>341.23</v>
       </c>
     </row>
     <row r="74">
@@ -6624,7 +6624,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1173041-58-CM25</t>
+          <t>3340-296-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6664,17 +6664,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>653.11</v>
+        <v>3244.71</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3340-296-CM25</t>
+          <t>1173041-58-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6729,17 +6729,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3244.71</v>
+        <v>653.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3185-115-CM25</t>
+          <t>3459-271-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6794,17 +6794,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>286.88</v>
+        <v>2639.82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>838099-83-CM25</t>
+          <t>3185-115-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6859,17 +6859,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>333.45</v>
+        <v>286.88</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3459-271-CM25</t>
+          <t>838099-83-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2639.82</v>
+        <v>333.45</v>
       </c>
     </row>
     <row r="101">
@@ -7079,7 +7079,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3340-304-CM25</t>
+          <t>5702-733-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1268.21</v>
+        <v>3763.53</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5702-733-CM25</t>
+          <t>3340-304-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3763.53</v>
+        <v>1268.21</v>
       </c>
     </row>
     <row r="105">
@@ -7534,7 +7534,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3340-331-CM25</t>
+          <t>3340-322-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3054.74</v>
+        <v>4177.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3340-322-CM25</t>
+          <t>837-568-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4177.45</v>
+        <v>276.11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>837-568-CM25</t>
+          <t>3340-331-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>276.11</v>
+        <v>3054.74</v>
       </c>
     </row>
     <row r="113">
@@ -8444,7 +8444,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1346279-200-CM25</t>
+          <t>3340-352-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8484,17 +8484,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1403.53</v>
+        <v>1225.45</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3340-352-CM25</t>
+          <t>1346279-200-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8549,17 +8549,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1225.45</v>
+        <v>1403.53</v>
       </c>
     </row>
     <row r="126">
@@ -8899,7 +8899,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>720-1086-CM25</t>
+          <t>1087-353-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1570.28</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1087-353-CM25</t>
+          <t>720-1086-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>275.85</v>
+        <v>1570.28</v>
       </c>
     </row>
     <row r="133">
@@ -10069,7 +10069,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5702-58-CM26</t>
+          <t>5702-61-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>400.08</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5702-61-CM26</t>
+          <t>5702-58-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1100.23</v>
+        <v>400.08</v>
       </c>
     </row>
     <row r="151">
@@ -10394,7 +10394,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1075963-2476-CM26</t>
+          <t>5702-85-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10414,17 +10414,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1756.55</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5702-85-CM26</t>
+          <t>1075963-2476-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10479,17 +10479,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3649.71</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="156">
@@ -10589,7 +10589,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1173041-5-CM26</t>
+          <t>3340-21-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10629,17 +10629,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>588.87</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="158">
@@ -10719,7 +10719,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3340-21-CM26</t>
+          <t>1173041-5-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10759,17 +10759,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4349.35</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="160">
@@ -10914,7 +10914,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3340-32-CM26</t>
+          <t>3340-33-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4847.94</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3340-33-CM26</t>
+          <t>1317925-11-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3387.89</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1317925-11-CM26</t>
+          <t>3340-32-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11084,17 +11084,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>608.37</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="165">
@@ -11434,7 +11434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5702-151-CM26</t>
+          <t>1173041-9-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3386</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1173041-9-CM26</t>
+          <t>5702-151-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>596.35</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="172">
@@ -11889,7 +11889,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5702-255-CM26</t>
+          <t>1079596-57-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11929,17 +11929,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4427.3</v>
+        <v>385.11</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1079596-57-CM26</t>
+          <t>5702-255-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11994,17 +11994,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>385.11</v>
+        <v>4427.3</v>
       </c>
     </row>
     <row r="179">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3483-119-CM26</t>
+          <t>5702-263-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12124,17 +12124,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1328.23</v>
+        <v>1281.94</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5702-263-CM26</t>
+          <t>3483-119-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12169,17 +12169,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1281.94</v>
+        <v>1328.23</v>
       </c>
     </row>
     <row r="182">
@@ -12799,7 +12799,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3340-114-CM26</t>
+          <t>4232-50-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1204.89</v>
+        <v>421.71</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4232-50-CM26</t>
+          <t>3340-114-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>421.71</v>
+        <v>1204.89</v>
       </c>
     </row>
     <row r="193">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5738-23-CM26</t>
+          <t>1193663-23-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13144,17 +13144,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13164,17 +13164,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>430.28</v>
+        <v>1292.25</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1193663-23-CM26</t>
+          <t>707409-53-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1292.25</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>707409-53-CM26</t>
+          <t>1173041-18-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>162.2</v>
+        <v>778.55</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1173041-18-CM26</t>
+          <t>5738-23-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>778.55</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="200">
@@ -13839,7 +13839,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1173457-25-CM26</t>
+          <t>1075963-7798-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13859,17 +13859,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>351.89</v>
+        <v>2111.32</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1075963-7798-CM26</t>
+          <t>1173457-25-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13924,17 +13924,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2111.32</v>
+        <v>351.89</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>707409-58-CM26</t>
+          <t>4232-66-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>148.2</v>
+        <v>426.83</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4232-66-CM26</t>
+          <t>707409-58-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>426.83</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="211">
@@ -14944,7 +14944,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5702-515-CM26</t>
+          <t>3185-97-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14964,17 +14964,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>426.59</v>
+        <v>471.22</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3185-97-CM26</t>
+          <t>5702-515-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15049,17 +15049,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>471.22</v>
+        <v>426.59</v>
       </c>
     </row>
     <row r="226">
@@ -15269,7 +15269,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3390-294-CM26</t>
+          <t>1173457-29-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15309,17 +15309,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1292.75</v>
+        <v>328.38</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1173457-29-CM26</t>
+          <t>3390-294-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15374,17 +15374,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>328.38</v>
+        <v>1292.75</v>
       </c>
     </row>
     <row r="231">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3340-247-CM26</t>
+          <t>3340-227-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -16089,17 +16089,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1548.26</v>
+        <v>1306.16</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3390-361-CM26</t>
+          <t>3340-247-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16129,17 +16129,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>516.63</v>
+        <v>1548.26</v>
       </c>
     </row>
     <row r="243">
@@ -16244,7 +16244,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1173041-56-CM26</t>
+          <t>3390-361-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16259,22 +16259,22 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>612.54</v>
+        <v>516.63</v>
       </c>
     </row>
     <row r="245">
@@ -16374,7 +16374,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1053139-139-CM26</t>
+          <t>1173041-56-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16389,22 +16389,22 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>172.73</v>
+        <v>612.54</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1075963-12353-CM26</t>
+          <t>1053139-139-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1683.64</v>
+        <v>172.73</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5702-688-CM26</t>
+          <t>1075963-12353-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4025.34</v>
+        <v>1683.64</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3483-318-CM26</t>
+          <t>3340-268-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1070.9</v>
+        <v>3995.57</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3340-268-CM26</t>
+          <t>3483-318-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -16674,17 +16674,17 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16693,72 +16693,1047 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3995.57</v>
+        <v>1070.9</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t>5702-688-CM26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>4025.34</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
           <t>1173041-60-CM26</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2239-1-LR25</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>597.42</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>3459-266-CM26</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>2314.73</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>837-667-CM26</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>61.003.000-9</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="n">
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>5702-718-CM26</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="n">
+        <v>67.89</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>5702-725-CM26</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>448.06</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>3185-132-CM26</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>61.102.001-5</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>1791.33</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1079596-198-CM26</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>535.5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>5702-760-CM26</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>1194.99</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>3340-283-CM26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>3189.1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1110404-1024-CM26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>227.42</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>5702-772-CM26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>4957.69</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1087-247-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>347.69</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1087-248-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>1582.65</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>5702-776-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>342.81</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1173041-69-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
         <is>
           <t>70.456.600-K</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G266" t="inlineStr">
         <is>
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
+      <c r="J266" t="inlineStr">
         <is>
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K266" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M251" s="2" t="n">
-        <v>597.42</v>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>680.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/arica-y-parinacota.xlsx
@@ -17499,7 +17499,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
